--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/119.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/119.xlsx
@@ -426,13 +426,13 @@
         <v>-8.962801420687379</v>
       </c>
       <c r="E2">
-        <v>-16.95078220088894</v>
+        <v>-16.02327826853393</v>
       </c>
       <c r="F2">
-        <v>1.899215192866378</v>
+        <v>1.571773155683372</v>
       </c>
       <c r="G2">
-        <v>-9.790209191326149</v>
+        <v>-11.57201749719453</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.357354081323662</v>
       </c>
       <c r="E3">
-        <v>-18.13248749319052</v>
+        <v>-17.1501935538167</v>
       </c>
       <c r="F3">
-        <v>2.107463444460562</v>
+        <v>2.058780292198035</v>
       </c>
       <c r="G3">
-        <v>-9.540032453526287</v>
+        <v>-9.971746055323989</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.704069158122395</v>
       </c>
       <c r="E4">
-        <v>-17.62163939733324</v>
+        <v>-17.62376325164284</v>
       </c>
       <c r="F4">
-        <v>2.428217243233364</v>
+        <v>1.940409903807597</v>
       </c>
       <c r="G4">
-        <v>-9.332383628358388</v>
+        <v>-9.87062865052658</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.070262405618466</v>
       </c>
       <c r="E5">
-        <v>-19.13309910992536</v>
+        <v>-18.33385967536361</v>
       </c>
       <c r="F5">
-        <v>2.220325189622383</v>
+        <v>1.370696909062626</v>
       </c>
       <c r="G5">
-        <v>-8.83725057625974</v>
+        <v>-9.921267742853491</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.463668735787576</v>
       </c>
       <c r="E6">
-        <v>-18.88851170029708</v>
+        <v>-18.79540627469937</v>
       </c>
       <c r="F6">
-        <v>2.316347882220096</v>
+        <v>1.873053693551163</v>
       </c>
       <c r="G6">
-        <v>-8.239832004488521</v>
+        <v>-9.319163586695385</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.908653633904683</v>
       </c>
       <c r="E7">
-        <v>-19.56727108388477</v>
+        <v>-19.57508270154799</v>
       </c>
       <c r="F7">
-        <v>2.29301442921804</v>
+        <v>1.813321776870097</v>
       </c>
       <c r="G7">
-        <v>-7.779043498452581</v>
+        <v>-8.452835783241435</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.408075534125513</v>
       </c>
       <c r="E8">
-        <v>-20.53881895443838</v>
+        <v>-19.73270076785897</v>
       </c>
       <c r="F8">
-        <v>2.082766498713498</v>
+        <v>1.58036829585482</v>
       </c>
       <c r="G8">
-        <v>-7.803130945920464</v>
+        <v>-9.050940130318576</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.97670591491401</v>
       </c>
       <c r="E9">
-        <v>-20.55517127408007</v>
+        <v>-19.78144979055154</v>
       </c>
       <c r="F9">
-        <v>2.468596840650229</v>
+        <v>2.110293147508525</v>
       </c>
       <c r="G9">
-        <v>-6.660858971760332</v>
+        <v>-8.067308656114477</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.612398465300307</v>
       </c>
       <c r="E10">
-        <v>-21.60974871556433</v>
+        <v>-20.49334854692736</v>
       </c>
       <c r="F10">
-        <v>2.875075068469141</v>
+        <v>2.255698134456728</v>
       </c>
       <c r="G10">
-        <v>-6.359783925130364</v>
+        <v>-7.431158545055574</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.318901681876276</v>
       </c>
       <c r="E11">
-        <v>-21.17311325174475</v>
+        <v>-22.86307635277122</v>
       </c>
       <c r="F11">
-        <v>2.647191195958997</v>
+        <v>2.372781239903216</v>
       </c>
       <c r="G11">
-        <v>-6.551312108776711</v>
+        <v>-7.422843929623941</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.097901235355627</v>
       </c>
       <c r="E12">
-        <v>-22.19119119272717</v>
+        <v>-21.61104838760453</v>
       </c>
       <c r="F12">
-        <v>3.23585392341041</v>
+        <v>2.738580001305449</v>
       </c>
       <c r="G12">
-        <v>-5.894431239905235</v>
+        <v>-6.983485081592734</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.94189368856453</v>
       </c>
       <c r="E13">
-        <v>-22.61375668780492</v>
+        <v>-23.16591805203418</v>
       </c>
       <c r="F13">
-        <v>3.466796128371689</v>
+        <v>2.890116563769174</v>
       </c>
       <c r="G13">
-        <v>-5.827520569865039</v>
+        <v>-5.88447601369388</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.850251407360437</v>
       </c>
       <c r="E14">
-        <v>-24.28996681327009</v>
+        <v>-24.05392463409429</v>
       </c>
       <c r="F14">
-        <v>3.528118510466131</v>
+        <v>3.007020741856657</v>
       </c>
       <c r="G14">
-        <v>-6.239395906114336</v>
+        <v>-6.425208201804132</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.811937523498336</v>
       </c>
       <c r="E15">
-        <v>-24.62171829059802</v>
+        <v>-25.67544437896883</v>
       </c>
       <c r="F15">
-        <v>4.28494479089026</v>
+        <v>3.106018930165226</v>
       </c>
       <c r="G15">
-        <v>-6.215134553903803</v>
+        <v>-6.343121882051503</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.814809857389722</v>
       </c>
       <c r="E16">
-        <v>-25.92571955195074</v>
+        <v>-25.25752962669696</v>
       </c>
       <c r="F16">
-        <v>4.657092160067549</v>
+        <v>3.943713749920254</v>
       </c>
       <c r="G16">
-        <v>-5.678100302491045</v>
+        <v>-6.813353743735526</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.850837466030844</v>
       </c>
       <c r="E17">
-        <v>-25.96753095246356</v>
+        <v>-27.03995963848605</v>
       </c>
       <c r="F17">
-        <v>5.017171872920855</v>
+        <v>4.54335234545876</v>
       </c>
       <c r="G17">
-        <v>-6.106821430226533</v>
+        <v>-6.336733343675264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.908934976678045</v>
       </c>
       <c r="E18">
-        <v>-26.78101696625345</v>
+        <v>-28.07715226825485</v>
       </c>
       <c r="F18">
-        <v>5.604535720284678</v>
+        <v>4.434090685029505</v>
       </c>
       <c r="G18">
-        <v>-6.701306589923608</v>
+        <v>-5.489827090631668</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.98301647448565</v>
       </c>
       <c r="E19">
-        <v>-27.52140888108553</v>
+        <v>-27.38776455617116</v>
       </c>
       <c r="F19">
-        <v>6.143032517822553</v>
+        <v>4.633385941734233</v>
       </c>
       <c r="G19">
-        <v>-6.404523381093393</v>
+        <v>-5.550418127948373</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.068204509026727</v>
       </c>
       <c r="E20">
-        <v>-28.64896268120339</v>
+        <v>-29.48596506051511</v>
       </c>
       <c r="F20">
-        <v>6.593167364503804</v>
+        <v>5.347016175571979</v>
       </c>
       <c r="G20">
-        <v>-7.174222490843255</v>
+        <v>-6.670735448654261</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.155972931229413</v>
       </c>
       <c r="E21">
-        <v>-29.10542833270256</v>
+        <v>-30.79353249514887</v>
       </c>
       <c r="F21">
-        <v>6.691975028309729</v>
+        <v>5.163108671741655</v>
       </c>
       <c r="G21">
-        <v>-6.895545062578056</v>
+        <v>-6.067371303417329</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.240589913451836</v>
       </c>
       <c r="E22">
-        <v>-29.45300003397627</v>
+        <v>-31.76990771899467</v>
       </c>
       <c r="F22">
-        <v>7.320760559283139</v>
+        <v>5.915572769422642</v>
       </c>
       <c r="G22">
-        <v>-6.587681168541597</v>
+        <v>-6.140700042827799</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.312833849448457</v>
       </c>
       <c r="E23">
-        <v>-30.01796112998821</v>
+        <v>-30.46770199758598</v>
       </c>
       <c r="F23">
-        <v>7.296877070325623</v>
+        <v>6.642501613544932</v>
       </c>
       <c r="G23">
-        <v>-7.42668952129161</v>
+        <v>-5.910227040492402</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.362460277345529</v>
       </c>
       <c r="E24">
-        <v>-29.48774701503713</v>
+        <v>-29.34041990590858</v>
       </c>
       <c r="F24">
-        <v>7.455262574475694</v>
+        <v>6.524424467215084</v>
       </c>
       <c r="G24">
-        <v>-7.653024903240548</v>
+        <v>-6.701162216174992</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.383179948113476</v>
       </c>
       <c r="E25">
-        <v>-30.12295832833005</v>
+        <v>-29.7534031499861</v>
       </c>
       <c r="F25">
-        <v>7.89529962251682</v>
+        <v>6.44999896954316</v>
       </c>
       <c r="G25">
-        <v>-7.594917750644341</v>
+        <v>-5.916549954437452</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.367745735898338</v>
       </c>
       <c r="E26">
-        <v>-30.08547162049456</v>
+        <v>-29.8835854565216</v>
       </c>
       <c r="F26">
-        <v>7.733811054075861</v>
+        <v>6.215456679849313</v>
       </c>
       <c r="G26">
-        <v>-7.259868935987881</v>
+        <v>-6.680625050434427</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.316190911067149</v>
       </c>
       <c r="E27">
-        <v>-29.08112401270339</v>
+        <v>-30.27042808438984</v>
       </c>
       <c r="F27">
-        <v>7.690606723815451</v>
+        <v>6.195390307883899</v>
       </c>
       <c r="G27">
-        <v>-7.692225657211234</v>
+        <v>-5.721645393806436</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.230730003814064</v>
       </c>
       <c r="E28">
-        <v>-30.69023573879691</v>
+        <v>-30.03819208761747</v>
       </c>
       <c r="F28">
-        <v>7.392006782863119</v>
+        <v>5.713653244785846</v>
       </c>
       <c r="G28">
-        <v>-7.338592003642079</v>
+        <v>-5.727328469547395</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.116618173581533</v>
       </c>
       <c r="E29">
-        <v>-29.49692396761367</v>
+        <v>-30.13517615120275</v>
       </c>
       <c r="F29">
-        <v>7.966366918737795</v>
+        <v>6.128416803367558</v>
       </c>
       <c r="G29">
-        <v>-7.683779792917222</v>
+        <v>-6.395414710044373</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.98362096436628</v>
       </c>
       <c r="E30">
-        <v>-29.63085585062753</v>
+        <v>-30.2819168229473</v>
       </c>
       <c r="F30">
-        <v>7.309721735273432</v>
+        <v>5.78473213815046</v>
       </c>
       <c r="G30">
-        <v>-7.093373191618538</v>
+        <v>-5.904242092367975</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.838192369398056</v>
       </c>
       <c r="E31">
-        <v>-29.38409250923856</v>
+        <v>-29.92993438799011</v>
       </c>
       <c r="F31">
-        <v>7.134411028349362</v>
+        <v>5.424665679175599</v>
       </c>
       <c r="G31">
-        <v>-7.117424545649267</v>
+        <v>-6.046391172766239</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.689434256874282</v>
       </c>
       <c r="E32">
-        <v>-27.63211195667704</v>
+        <v>-30.00843322067607</v>
       </c>
       <c r="F32">
-        <v>6.951225860894279</v>
+        <v>5.705970965492283</v>
       </c>
       <c r="G32">
-        <v>-6.80038963735416</v>
+        <v>-5.400184117627638</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.543409604452411</v>
       </c>
       <c r="E33">
-        <v>-28.22844858485112</v>
+        <v>-29.23826206076955</v>
       </c>
       <c r="F33">
-        <v>6.732984184952722</v>
+        <v>5.020031397195319</v>
       </c>
       <c r="G33">
-        <v>-7.02865437758005</v>
+        <v>-5.623776398352879</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.402315170790829</v>
       </c>
       <c r="E34">
-        <v>-28.07078976227408</v>
+        <v>-29.02308256134708</v>
       </c>
       <c r="F34">
-        <v>6.9261992249209</v>
+        <v>5.364171664483957</v>
       </c>
       <c r="G34">
-        <v>-7.29651689958532</v>
+        <v>-5.520585261529902</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.268567551060958</v>
       </c>
       <c r="E35">
-        <v>-27.30974347749301</v>
+        <v>-28.28264083330091</v>
       </c>
       <c r="F35">
-        <v>6.276961302772372</v>
+        <v>5.309903659191756</v>
       </c>
       <c r="G35">
-        <v>-6.871500270990445</v>
+        <v>-5.495342824073093</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.137311996718396</v>
       </c>
       <c r="E36">
-        <v>-26.81863047136116</v>
+        <v>-27.59222062914347</v>
       </c>
       <c r="F36">
-        <v>6.366633730860223</v>
+        <v>5.580175091703151</v>
       </c>
       <c r="G36">
-        <v>-6.670535294139134</v>
+        <v>-5.889535657338544</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.005162839019423</v>
       </c>
       <c r="E37">
-        <v>-25.80213749628142</v>
+        <v>-27.16376811785576</v>
       </c>
       <c r="F37">
-        <v>5.95606005460187</v>
+        <v>5.525794428444168</v>
       </c>
       <c r="G37">
-        <v>-6.273727327290807</v>
+        <v>-5.439453777251072</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.863960027273673</v>
       </c>
       <c r="E38">
-        <v>-26.13094093703035</v>
+        <v>-27.10766032490072</v>
       </c>
       <c r="F38">
-        <v>6.042866331476037</v>
+        <v>5.062034594721671</v>
       </c>
       <c r="G38">
-        <v>-6.941442789751568</v>
+        <v>-5.567139233015303</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.701442673551276</v>
       </c>
       <c r="E39">
-        <v>-25.3458756261126</v>
+        <v>-26.58433628315231</v>
       </c>
       <c r="F39">
-        <v>5.988159291460351</v>
+        <v>4.771058947344705</v>
       </c>
       <c r="G39">
-        <v>-6.228364439231484</v>
+        <v>-5.708195666634272</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.511275982454034</v>
       </c>
       <c r="E40">
-        <v>-25.4078659068036</v>
+        <v>-25.51409032160152</v>
       </c>
       <c r="F40">
-        <v>5.86496780478562</v>
+        <v>5.283525127617009</v>
       </c>
       <c r="G40">
-        <v>-6.481333496578434</v>
+        <v>-5.399370374680895</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.283273064697663</v>
       </c>
       <c r="E41">
-        <v>-24.81047867265974</v>
+        <v>-23.1916760121898</v>
       </c>
       <c r="F41">
-        <v>5.712675771250542</v>
+        <v>5.159603020893008</v>
       </c>
       <c r="G41">
-        <v>-5.726498320492855</v>
+        <v>-5.743045520817135</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.01567231554677</v>
       </c>
       <c r="E42">
-        <v>-24.01318648192128</v>
+        <v>-24.60993520123006</v>
       </c>
       <c r="F42">
-        <v>5.421604033254853</v>
+        <v>5.196594595632423</v>
       </c>
       <c r="G42">
-        <v>-6.136598515878493</v>
+        <v>-5.99095493451942</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.709767719055015</v>
       </c>
       <c r="E43">
-        <v>-23.54045455178657</v>
+        <v>-23.73689975423931</v>
       </c>
       <c r="F43">
-        <v>5.714677106895706</v>
+        <v>5.13311514482109</v>
       </c>
       <c r="G43">
-        <v>-5.598642241207532</v>
+        <v>-5.58346987271666</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.367686765187397</v>
       </c>
       <c r="E44">
-        <v>-23.52746688833257</v>
+        <v>-23.2388491259277</v>
       </c>
       <c r="F44">
-        <v>5.24389603106708</v>
+        <v>5.102685896646654</v>
       </c>
       <c r="G44">
-        <v>-5.910456726001564</v>
+        <v>-5.272400225216622</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.001853133160952</v>
       </c>
       <c r="E45">
-        <v>-23.41203155740304</v>
+        <v>-22.74061283018179</v>
       </c>
       <c r="F45">
-        <v>5.450343411927578</v>
+        <v>4.783838999635096</v>
       </c>
       <c r="G45">
-        <v>-5.129384902326665</v>
+        <v>-5.833676141510558</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6206171109030022</v>
       </c>
       <c r="E46">
-        <v>-22.17062739225835</v>
+        <v>-21.39492696558846</v>
       </c>
       <c r="F46">
-        <v>5.420745844625552</v>
+        <v>4.91220943931213</v>
       </c>
       <c r="G46">
-        <v>-5.8055331041952</v>
+        <v>-5.784441412011089</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2367597325238915</v>
       </c>
       <c r="E47">
-        <v>-22.32929153606509</v>
+        <v>-22.53910026531447</v>
       </c>
       <c r="F47">
-        <v>4.91118557720227</v>
+        <v>4.691366689725782</v>
       </c>
       <c r="G47">
-        <v>-5.475744087698531</v>
+        <v>-5.138211388321571</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.135850532931324</v>
       </c>
       <c r="E48">
-        <v>-20.64097679957741</v>
+        <v>-21.1157601284376</v>
       </c>
       <c r="F48">
-        <v>5.215201384234105</v>
+        <v>4.473476241563011</v>
       </c>
       <c r="G48">
-        <v>-5.582485506248826</v>
+        <v>-6.122456450957286</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.4882769506274868</v>
       </c>
       <c r="E49">
-        <v>-21.22795760045165</v>
+        <v>-20.94627746022653</v>
       </c>
       <c r="F49">
-        <v>4.606994156281041</v>
+        <v>4.810045230790061</v>
       </c>
       <c r="G49">
-        <v>-5.248936209845033</v>
+        <v>-5.145101953596405</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.8068937680257559</v>
       </c>
       <c r="E50">
-        <v>-20.60121226931606</v>
+        <v>-20.77492000377629</v>
       </c>
       <c r="F50">
-        <v>4.856819824556538</v>
+        <v>4.045188756763194</v>
       </c>
       <c r="G50">
-        <v>-5.102944819000659</v>
+        <v>-6.060539800130565</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.084256339512463</v>
       </c>
       <c r="E51">
-        <v>-20.88818166718213</v>
+        <v>-19.96946750287601</v>
       </c>
       <c r="F51">
-        <v>4.796057418826389</v>
+        <v>4.482412669104412</v>
       </c>
       <c r="G51">
-        <v>-4.834275116491767</v>
+        <v>-5.988953389368159</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.314157544727513</v>
       </c>
       <c r="E52">
-        <v>-19.78084750350852</v>
+        <v>-18.96804076081978</v>
       </c>
       <c r="F52">
-        <v>4.664882127123476</v>
+        <v>4.609118090301819</v>
       </c>
       <c r="G52">
-        <v>-5.080478294983141</v>
+        <v>-5.785760463077986</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.490119020955957</v>
       </c>
       <c r="E53">
-        <v>-19.35095040901236</v>
+        <v>-20.09241557218426</v>
       </c>
       <c r="F53">
-        <v>4.904252142040837</v>
+        <v>4.569727563563896</v>
       </c>
       <c r="G53">
-        <v>-5.293314731436523</v>
+        <v>-6.047142572503352</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.611803044938976</v>
       </c>
       <c r="E54">
-        <v>-18.73866449538327</v>
+        <v>-18.82632216674974</v>
       </c>
       <c r="F54">
-        <v>4.87903663829962</v>
+        <v>4.603544834415784</v>
       </c>
       <c r="G54">
-        <v>-5.433990543354597</v>
+        <v>-5.681972143931191</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.678822074477327</v>
       </c>
       <c r="E55">
-        <v>-18.39077806516601</v>
+        <v>-18.67702290719086</v>
       </c>
       <c r="F55">
-        <v>4.787647832953168</v>
+        <v>4.557828894190084</v>
       </c>
       <c r="G55">
-        <v>-5.462615920239192</v>
+        <v>-6.520386595578945</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.694183701919976</v>
       </c>
       <c r="E56">
-        <v>-18.29611484450967</v>
+        <v>-17.22090114697247</v>
       </c>
       <c r="F56">
-        <v>4.73925129581201</v>
+        <v>4.200169670887758</v>
       </c>
       <c r="G56">
-        <v>-5.195504797971036</v>
+        <v>-5.60438766015812</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.662804347656599</v>
       </c>
       <c r="E57">
-        <v>-17.85626869261866</v>
+        <v>-17.34399865592297</v>
       </c>
       <c r="F57">
-        <v>4.865554130451656</v>
+        <v>4.326737583096301</v>
       </c>
       <c r="G57">
-        <v>-5.296527047343219</v>
+        <v>-5.882182439823828</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.589284995511544</v>
       </c>
       <c r="E58">
-        <v>-17.56650975476386</v>
+        <v>-19.21145076720607</v>
       </c>
       <c r="F58">
-        <v>4.506552951956795</v>
+        <v>4.521518237455771</v>
       </c>
       <c r="G58">
-        <v>-5.879311370959314</v>
+        <v>-5.725041458120462</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.478810057940582</v>
       </c>
       <c r="E59">
-        <v>-18.8212774467052</v>
+        <v>-17.86331046970059</v>
       </c>
       <c r="F59">
-        <v>4.699907157648645</v>
+        <v>4.613659200403966</v>
       </c>
       <c r="G59">
-        <v>-5.804634049487912</v>
+        <v>-6.300265847263596</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.336150446899429</v>
       </c>
       <c r="E60">
-        <v>-17.61515462255426</v>
+        <v>-15.89225593007</v>
       </c>
       <c r="F60">
-        <v>4.549230440549025</v>
+        <v>5.160012234389991</v>
       </c>
       <c r="G60">
-        <v>-6.228006786081504</v>
+        <v>-6.691856671832406</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.166256144182601</v>
       </c>
       <c r="E61">
-        <v>-18.07819108983855</v>
+        <v>-17.09136867645707</v>
       </c>
       <c r="F61">
-        <v>4.596820147839857</v>
+        <v>4.051456184532775</v>
       </c>
       <c r="G61">
-        <v>-5.574817291464404</v>
+        <v>-6.182105777686433</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.9730597748399368</v>
       </c>
       <c r="E62">
-        <v>-17.60869701861932</v>
+        <v>-16.10422474142104</v>
       </c>
       <c r="F62">
-        <v>4.459504996947394</v>
+        <v>4.700026442554647</v>
       </c>
       <c r="G62">
-        <v>-6.252510948687437</v>
+        <v>-6.071302206845544</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.7634510061255544</v>
       </c>
       <c r="E63">
-        <v>-16.50078773874673</v>
+        <v>-17.01654470042833</v>
       </c>
       <c r="F63">
-        <v>4.513227936488553</v>
+        <v>4.343724085058107</v>
       </c>
       <c r="G63">
-        <v>-5.981777357817654</v>
+        <v>-6.988613630890146</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.5425636675327214</v>
       </c>
       <c r="E64">
-        <v>-15.99676858169302</v>
+        <v>-15.69505447245798</v>
       </c>
       <c r="F64">
-        <v>4.486408713455517</v>
+        <v>5.039729974033891</v>
       </c>
       <c r="G64">
-        <v>-6.281123200685795</v>
+        <v>-7.272002893314708</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.3164099789139523</v>
       </c>
       <c r="E65">
-        <v>-16.72095308805165</v>
+        <v>-16.12316281972111</v>
       </c>
       <c r="F65">
-        <v>4.415709212361384</v>
+        <v>3.940761448496677</v>
       </c>
       <c r="G65">
-        <v>-6.461846321736892</v>
+        <v>-7.448516207105036</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.09293930162330472</v>
       </c>
       <c r="E66">
-        <v>-16.24775472509415</v>
+        <v>-14.84583879874757</v>
       </c>
       <c r="F66">
-        <v>4.462475522453833</v>
+        <v>4.303233486409267</v>
       </c>
       <c r="G66">
-        <v>-6.406669299993269</v>
+        <v>-7.240175044188094</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1222862187491738</v>
       </c>
       <c r="E67">
-        <v>-16.29152695485229</v>
+        <v>-15.94247670681506</v>
       </c>
       <c r="F67">
-        <v>4.536872855634063</v>
+        <v>4.328833352625383</v>
       </c>
       <c r="G67">
-        <v>-7.054753213863873</v>
+        <v>-7.181516646369901</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.3211356146948411</v>
       </c>
       <c r="E68">
-        <v>-16.26611315872124</v>
+        <v>-16.65948358187153</v>
       </c>
       <c r="F68">
-        <v>4.148751249461188</v>
+        <v>4.143272427459072</v>
       </c>
       <c r="G68">
-        <v>-6.488312654835372</v>
+        <v>-6.127686718123042</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.4966539601349494</v>
       </c>
       <c r="E69">
-        <v>-17.04303174489919</v>
+        <v>-15.1031466918634</v>
       </c>
       <c r="F69">
-        <v>4.325731945069302</v>
+        <v>3.758992789300381</v>
       </c>
       <c r="G69">
-        <v>-6.221240907225929</v>
+        <v>-6.788235992697977</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6430315931135049</v>
       </c>
       <c r="E70">
-        <v>-16.2546380055858</v>
+        <v>-15.92770029612804</v>
       </c>
       <c r="F70">
-        <v>4.347730069818046</v>
+        <v>4.288392456020712</v>
       </c>
       <c r="G70">
-        <v>-6.915419421563612</v>
+        <v>-7.41735444595499</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.7528399415425905</v>
       </c>
       <c r="E71">
-        <v>-16.32776833233567</v>
+        <v>-14.60178574905219</v>
       </c>
       <c r="F71">
-        <v>3.979325264566605</v>
+        <v>4.247515838162167</v>
       </c>
       <c r="G71">
-        <v>-6.185199969616988</v>
+        <v>-5.750198583816724</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.8202600575013815</v>
       </c>
       <c r="E72">
-        <v>-16.57511811110864</v>
+        <v>-16.12500138016823</v>
       </c>
       <c r="F72">
-        <v>4.332078896109552</v>
+        <v>4.416535923029379</v>
       </c>
       <c r="G72">
-        <v>-6.689556535519236</v>
+        <v>-7.169563156228844</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.8403027943385954</v>
       </c>
       <c r="E73">
-        <v>-17.04101204549177</v>
+        <v>-15.53917081169194</v>
       </c>
       <c r="F73">
-        <v>3.877505656884101</v>
+        <v>4.0452202347245</v>
       </c>
       <c r="G73">
-        <v>-6.343994686986315</v>
+        <v>-6.384271681628499</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8081699390716645</v>
       </c>
       <c r="E74">
-        <v>-16.19390211219493</v>
+        <v>-15.71124829550941</v>
       </c>
       <c r="F74">
-        <v>4.107904452829144</v>
+        <v>4.027834459674544</v>
       </c>
       <c r="G74">
-        <v>-6.654552463923079</v>
+        <v>-5.478392033497002</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.7201703335576579</v>
       </c>
       <c r="E75">
-        <v>-16.7140154658719</v>
+        <v>-15.40617858703468</v>
       </c>
       <c r="F75">
-        <v>3.968861327534442</v>
+        <v>4.295445176088147</v>
       </c>
       <c r="G75">
-        <v>-6.112770284913806</v>
+        <v>-7.463957635763783</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5762123160169531</v>
       </c>
       <c r="E76">
-        <v>-17.31721726064161</v>
+        <v>-16.71078666390443</v>
       </c>
       <c r="F76">
-        <v>3.976901461546014</v>
+        <v>3.699756236326189</v>
       </c>
       <c r="G76">
-        <v>-5.945549390579825</v>
+        <v>-6.174837871932263</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3738526984622551</v>
       </c>
       <c r="E77">
-        <v>-18.16263807313359</v>
+        <v>-16.22005857806323</v>
       </c>
       <c r="F77">
-        <v>3.596655972638957</v>
+        <v>3.963201921438515</v>
       </c>
       <c r="G77">
-        <v>-5.947829839563639</v>
+        <v>-6.03965154368314</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.1150383149586987</v>
       </c>
       <c r="E78">
-        <v>-18.57351104832353</v>
+        <v>-18.3587708108798</v>
       </c>
       <c r="F78">
-        <v>4.041033665870751</v>
+        <v>3.865027130328329</v>
       </c>
       <c r="G78">
-        <v>-5.502502449515802</v>
+        <v>-5.769610290562399</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.1962354573154738</v>
       </c>
       <c r="E79">
-        <v>-17.97707026524727</v>
+        <v>-17.4800430720614</v>
       </c>
       <c r="F79">
-        <v>3.57503558342589</v>
+        <v>3.810474166649565</v>
       </c>
       <c r="G79">
-        <v>-5.097219087379429</v>
+        <v>-5.434833817295374</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5579302166840385</v>
       </c>
       <c r="E80">
-        <v>-18.96466704768407</v>
+        <v>-16.33414895221248</v>
       </c>
       <c r="F80">
-        <v>3.283365764165378</v>
+        <v>3.973346108653198</v>
       </c>
       <c r="G80">
-        <v>-4.917713299526887</v>
+        <v>-5.61673817810787</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.9593278932443224</v>
       </c>
       <c r="E81">
-        <v>-18.85851055999626</v>
+        <v>-17.94672043244787</v>
       </c>
       <c r="F81">
-        <v>3.581142307919327</v>
+        <v>2.853482843747769</v>
       </c>
       <c r="G81">
-        <v>-4.403024166933948</v>
+        <v>-4.97619451138087</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.394979992142494</v>
       </c>
       <c r="E82">
-        <v>-18.93596557942346</v>
+        <v>-19.11619431645473</v>
       </c>
       <c r="F82">
-        <v>3.476718313122422</v>
+        <v>3.756118354412667</v>
       </c>
       <c r="G82">
-        <v>-4.186319170261981</v>
+        <v>-4.792049076243273</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.855188391614621</v>
       </c>
       <c r="E83">
-        <v>-20.2925197816352</v>
+        <v>-19.08333570905507</v>
       </c>
       <c r="F83">
-        <v>3.751603752067409</v>
+        <v>3.745031485093598</v>
       </c>
       <c r="G83">
-        <v>-4.19175943560754</v>
+        <v>-5.163063360412806</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.325623026019951</v>
       </c>
       <c r="E84">
-        <v>-20.9210493315298</v>
+        <v>-19.53486985235988</v>
       </c>
       <c r="F84">
-        <v>3.600408476973638</v>
+        <v>3.106635235512909</v>
       </c>
       <c r="G84">
-        <v>-4.636555267762748</v>
+        <v>-4.11110044723327</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.79824017457554</v>
       </c>
       <c r="E85">
-        <v>-22.38877304215584</v>
+        <v>-21.60090913430135</v>
       </c>
       <c r="F85">
-        <v>3.410753760102692</v>
+        <v>2.887493952571911</v>
       </c>
       <c r="G85">
-        <v>-3.70904580711139</v>
+        <v>-5.196390727792085</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.257906563873858</v>
       </c>
       <c r="E86">
-        <v>-23.22561692487729</v>
+        <v>-21.11856778232236</v>
       </c>
       <c r="F86">
-        <v>3.161599069423462</v>
+        <v>2.927656517729242</v>
       </c>
       <c r="G86">
-        <v>-4.316632884495328</v>
+        <v>-4.462046780345239</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.693339972570532</v>
       </c>
       <c r="E87">
-        <v>-24.35779882543099</v>
+        <v>-22.98122876810535</v>
       </c>
       <c r="F87">
-        <v>2.792239984923996</v>
+        <v>2.659073297984753</v>
       </c>
       <c r="G87">
-        <v>-3.579614741477534</v>
+        <v>-4.354278339446837</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.093897312226496</v>
       </c>
       <c r="E88">
-        <v>-25.18973837080213</v>
+        <v>-22.71501336661643</v>
       </c>
       <c r="F88">
-        <v>2.580887012304119</v>
+        <v>2.86670690096606</v>
       </c>
       <c r="G88">
-        <v>-3.231352447601191</v>
+        <v>-4.054397657464507</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.444825657613123</v>
       </c>
       <c r="E89">
-        <v>-26.99080305313279</v>
+        <v>-25.09565932329278</v>
       </c>
       <c r="F89">
-        <v>2.547020039408064</v>
+        <v>2.610834150650126</v>
       </c>
       <c r="G89">
-        <v>-3.29091974379135</v>
+        <v>-2.279850694907175</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.738769909134257</v>
       </c>
       <c r="E90">
-        <v>-27.29796038812505</v>
+        <v>-27.32934724147222</v>
       </c>
       <c r="F90">
-        <v>2.128783964673816</v>
+        <v>2.42734911419523</v>
       </c>
       <c r="G90">
-        <v>-2.928187262837856</v>
+        <v>-3.385008772008427</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.966241632879387</v>
       </c>
       <c r="E91">
-        <v>-29.20320714347617</v>
+        <v>-27.50464447030913</v>
       </c>
       <c r="F91">
-        <v>1.990749790875723</v>
+        <v>2.003403931320888</v>
       </c>
       <c r="G91">
-        <v>-3.196092440723398</v>
+        <v>-3.31172268847823</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.120133706130155</v>
       </c>
       <c r="E92">
-        <v>-30.32609208689212</v>
+        <v>-30.998468586366</v>
       </c>
       <c r="F92">
-        <v>1.50747693461288</v>
+        <v>2.202525230871028</v>
       </c>
       <c r="G92">
-        <v>-3.161777425654725</v>
+        <v>-3.739151014919296</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.194348518098538</v>
       </c>
       <c r="E93">
-        <v>-32.54883241915801</v>
+        <v>-32.81166957903721</v>
       </c>
       <c r="F93">
-        <v>0.7665155466871671</v>
+        <v>0.7121920407789784</v>
       </c>
       <c r="G93">
-        <v>-3.285495884553588</v>
+        <v>-4.133307754747592</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.181280718119583</v>
       </c>
       <c r="E94">
-        <v>-34.52002281300883</v>
+        <v>-33.54928101082858</v>
       </c>
       <c r="F94">
-        <v>0.7049893862116366</v>
+        <v>0.9581500616508049</v>
       </c>
       <c r="G94">
-        <v>-3.521760242941405</v>
+        <v>-3.889542523874885</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.079664666184499</v>
       </c>
       <c r="E95">
-        <v>-36.41682849280965</v>
+        <v>-36.00974358612713</v>
       </c>
       <c r="F95">
-        <v>0.4812780003093938</v>
+        <v>-0.1248723913825192</v>
       </c>
       <c r="G95">
-        <v>-2.946181481869851</v>
+        <v>-3.615908333146552</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.880522360429873</v>
       </c>
       <c r="E96">
-        <v>-37.77744700044327</v>
+        <v>-38.64179683428731</v>
       </c>
       <c r="F96">
-        <v>-0.2749477137477057</v>
+        <v>-0.4558258779859917</v>
       </c>
       <c r="G96">
-        <v>-3.341398056261848</v>
+        <v>-3.831553495254818</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.594398714019746</v>
       </c>
       <c r="E97">
-        <v>-40.72385785726792</v>
+        <v>-38.80549437695359</v>
       </c>
       <c r="F97">
-        <v>-0.6602197360549501</v>
+        <v>-0.9739150161884977</v>
       </c>
       <c r="G97">
-        <v>-3.07187195492594</v>
+        <v>-3.865389451975812</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.211058221471286</v>
       </c>
       <c r="E98">
-        <v>-41.97491446475997</v>
+        <v>-41.74130181188927</v>
       </c>
       <c r="F98">
-        <v>-1.477250102579742</v>
+        <v>-1.403265296366107</v>
       </c>
       <c r="G98">
-        <v>-4.244022732606376</v>
+        <v>-3.629105406258639</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.764014347879691</v>
       </c>
       <c r="E99">
-        <v>-44.41745560417316</v>
+        <v>-42.85672609437758</v>
       </c>
       <c r="F99">
-        <v>-2.076206123378341</v>
+        <v>-2.187507224353288</v>
       </c>
       <c r="G99">
-        <v>-4.165716380090227</v>
+        <v>-4.204172296766919</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.232959447771921</v>
       </c>
       <c r="E100">
-        <v>-46.92191230445623</v>
+        <v>-46.05059088487737</v>
       </c>
       <c r="F100">
-        <v>-2.427031315607571</v>
+        <v>-2.373730015074436</v>
       </c>
       <c r="G100">
-        <v>-4.632821237628099</v>
+        <v>-4.919855937205204</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.692861700676914</v>
       </c>
       <c r="E101">
-        <v>-48.73323850888826</v>
+        <v>-48.96968938284326</v>
       </c>
       <c r="F101">
-        <v>-3.00046616509332</v>
+        <v>-2.92436405179813</v>
       </c>
       <c r="G101">
-        <v>-4.446664413674562</v>
+        <v>-4.174884113127316</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.064878298258563</v>
       </c>
       <c r="E102">
-        <v>-50.53912941239259</v>
+        <v>-50.82440176462428</v>
       </c>
       <c r="F102">
-        <v>-3.356060268460467</v>
+        <v>-3.231926928048753</v>
       </c>
       <c r="G102">
-        <v>-4.699387379404554</v>
+        <v>-4.555502532801344</v>
       </c>
     </row>
   </sheetData>
